--- a/results/all_results_lstm.xlsx
+++ b/results/all_results_lstm.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+        <bgColor rgb="000070C0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1579,137 +1593,137 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>2026-05-23_08-56-12</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="1" t="n">
         <v>0.289440167738663</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="1" t="n">
         <v>256</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.003535634629148813</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="1" t="n">
         <v>0.4871572058385361</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="1" t="n">
         <v>0.2765925722720768</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="1" t="n">
         <v>0.9059931737548839</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="1" t="n">
         <v>0.9101195257349193</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="1" t="n">
         <v>0.9059931737548839</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9" s="1" t="n">
         <v>0.905838374656336</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.9835167441417632</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W9" s="1" t="n">
         <v>0.4871572058385361</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9" s="1" t="n">
         <v>0.8850424217031528</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9" s="1" t="n">
         <v>0.8888434466916388</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9" s="1" t="n">
         <v>0.8850424217031528</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="1" t="n">
         <v>0.878022257698333</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB9" s="1" t="n">
         <v>0.9690265586682292</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9" s="1" t="n">
         <v>0.1896505658359691</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.9430711218183723</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9" s="1" t="n">
         <v>0.9431243177502904</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF9" s="1" t="n">
         <v>0.9430711218183723</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG9" s="1" t="n">
         <v>0.942716677341435</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH9" s="1" t="n">
         <v>0.9919684106686006</v>
       </c>
-      <c r="AI9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AI9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK9" s="1" t="n">
         <v>327.0158111779965</v>
       </c>
-      <c r="AL9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AL9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="1" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="AN9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="1" t="n">
         <v>92000</v>
       </c>
-      <c r="AP9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="b">
+      <c r="AP9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4279,137 +4293,137 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-05-23_09-53-32</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="D29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="2" t="n">
         <v>0.4526941447419411</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="2" t="n">
         <v>0.001502900296524595</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="2" t="n">
         <v>0.5335694702867564</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="2" t="n">
         <v>0.3171811952727125</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" s="2" t="n">
         <v>0.8933731490732737</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="2" t="n">
         <v>0.8994429034785064</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" s="2" t="n">
         <v>0.8933731490732737</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U29" s="2" t="n">
         <v>0.8927242919042692</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29" s="2" t="n">
         <v>0.9805210784076335</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W29" s="2" t="n">
         <v>0.5335694702867564</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X29" s="2" t="n">
         <v>0.8894417094375197</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29" s="2" t="n">
         <v>0.8935509278571486</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z29" s="2" t="n">
         <v>0.8894417094375197</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA29" s="2" t="n">
         <v>0.8813942297890893</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AB29" s="2" t="n">
         <v>0.9620793900733482</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC29" s="2" t="n">
         <v>0.2390158722715436</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD29" s="2" t="n">
         <v>0.9344820362417513</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE29" s="2" t="n">
         <v>0.9343272772938765</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF29" s="2" t="n">
         <v>0.9344820362417513</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG29" s="2" t="n">
         <v>0.9324290198880442</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH29" s="2" t="n">
         <v>0.9861238747763847</v>
       </c>
-      <c r="AI29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
+      <c r="AI29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AK29" s="2" t="n">
         <v>49.0435889970031</v>
       </c>
-      <c r="AL29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AL29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="n">
+      <c r="AN29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="2" t="n">
         <v>92000</v>
       </c>
-      <c r="AP29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" t="b">
+      <c r="AP29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ29" s="2" t="b">
         <v>0</v>
       </c>
     </row>

--- a/results/all_results_lstm.xlsx
+++ b/results/all_results_lstm.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000070C0"/>
-        <bgColor rgb="000070C0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +632,51 @@
           <t>cudnn_benchmark</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>train_macro_precision</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>train_macro_recall</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>train_macro_f1</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>val_macro_precision</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>val_macro_recall</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>val_macro_f1</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>test_macro_precision</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>test_macro_recall</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>test_macro_f1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -781,6 +812,33 @@
       <c r="AQ2" t="b">
         <v>0</v>
       </c>
+      <c r="AR2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -916,6 +974,33 @@
       <c r="AQ3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1051,6 +1136,33 @@
       <c r="AQ4" t="b">
         <v>0</v>
       </c>
+      <c r="AR4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1186,6 +1298,33 @@
       <c r="AQ5" t="b">
         <v>0</v>
       </c>
+      <c r="AR5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1321,6 +1460,33 @@
       <c r="AQ6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1456,6 +1622,33 @@
       <c r="AQ7" t="b">
         <v>0</v>
       </c>
+      <c r="AR7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1591,140 +1784,194 @@
       <c r="AQ8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-05-23_08-56-12</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" t="n">
         <v>42</v>
       </c>
-      <c r="D9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="n">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" t="n">
         <v>0.289440167738663</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9" t="n">
         <v>256</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="L9" t="n">
         <v>0.003535634629148813</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" t="n">
         <v>38</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9" t="n">
         <v>10</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P9" t="n">
         <v>0.4871572058385361</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="Q9" t="n">
         <v>0.2765925722720768</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="R9" t="n">
         <v>0.9059931737548839</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="S9" t="n">
         <v>0.9101195257349193</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="T9" t="n">
         <v>0.9059931737548839</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="U9" t="n">
         <v>0.905838374656336</v>
       </c>
-      <c r="V9" s="1" t="n">
+      <c r="V9" t="n">
         <v>0.9835167441417632</v>
       </c>
-      <c r="W9" s="1" t="n">
+      <c r="W9" t="n">
         <v>0.4871572058385361</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="X9" t="n">
         <v>0.8850424217031528</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Y9" t="n">
         <v>0.8888434466916388</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="Z9" t="n">
         <v>0.8850424217031528</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AA9" t="n">
         <v>0.878022257698333</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AB9" t="n">
         <v>0.9690265586682292</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AC9" t="n">
         <v>0.1896505658359691</v>
       </c>
-      <c r="AD9" s="1" t="n">
+      <c r="AD9" t="n">
         <v>0.9430711218183723</v>
       </c>
-      <c r="AE9" s="1" t="n">
+      <c r="AE9" t="n">
         <v>0.9431243177502904</v>
       </c>
-      <c r="AF9" s="1" t="n">
+      <c r="AF9" t="n">
         <v>0.9430711218183723</v>
       </c>
-      <c r="AG9" s="1" t="n">
+      <c r="AG9" t="n">
         <v>0.942716677341435</v>
       </c>
-      <c r="AH9" s="1" t="n">
+      <c r="AH9" t="n">
         <v>0.9919684106686006</v>
       </c>
-      <c r="AI9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="1" t="n">
+      <c r="AI9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>18</v>
       </c>
-      <c r="AK9" s="1" t="n">
+      <c r="AK9" t="n">
         <v>327.0158111779965</v>
       </c>
-      <c r="AL9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="1" t="inlineStr">
+      <c r="AL9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="1" t="n">
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
         <v>92000</v>
       </c>
-      <c r="AP9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="1" t="b">
-        <v>0</v>
+      <c r="AP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -1861,6 +2108,33 @@
       <c r="AQ10" t="b">
         <v>0</v>
       </c>
+      <c r="AR10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1996,6 +2270,33 @@
       <c r="AQ11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2131,6 +2432,33 @@
       <c r="AQ12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2266,6 +2594,33 @@
       <c r="AQ13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2401,6 +2756,33 @@
       <c r="AQ14" t="b">
         <v>0</v>
       </c>
+      <c r="AR14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2536,6 +2918,33 @@
       <c r="AQ15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2671,6 +3080,33 @@
       <c r="AQ16" t="b">
         <v>0</v>
       </c>
+      <c r="AR16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2806,6 +3242,33 @@
       <c r="AQ17" t="b">
         <v>0</v>
       </c>
+      <c r="AR17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2941,6 +3404,33 @@
       <c r="AQ18" t="b">
         <v>0</v>
       </c>
+      <c r="AR18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3076,6 +3566,33 @@
       <c r="AQ19" t="b">
         <v>0</v>
       </c>
+      <c r="AR19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3211,6 +3728,33 @@
       <c r="AQ20" t="b">
         <v>0</v>
       </c>
+      <c r="AR20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3346,6 +3890,33 @@
       <c r="AQ21" t="b">
         <v>0</v>
       </c>
+      <c r="AR21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3481,6 +4052,33 @@
       <c r="AQ22" t="b">
         <v>0</v>
       </c>
+      <c r="AR22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3616,6 +4214,33 @@
       <c r="AQ23" t="b">
         <v>0</v>
       </c>
+      <c r="AR23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3751,6 +4376,33 @@
       <c r="AQ24" t="b">
         <v>0</v>
       </c>
+      <c r="AR24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3886,6 +4538,33 @@
       <c r="AQ25" t="b">
         <v>0</v>
       </c>
+      <c r="AR25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4021,6 +4700,33 @@
       <c r="AQ26" t="b">
         <v>0</v>
       </c>
+      <c r="AR26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4156,6 +4862,33 @@
       <c r="AQ27" t="b">
         <v>0</v>
       </c>
+      <c r="AR27" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.77</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4291,140 +5024,194 @@
       <c r="AQ28" t="b">
         <v>0</v>
       </c>
+      <c r="AR28" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-05-23_09-53-32</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
         <v>100</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" t="n">
         <v>42</v>
       </c>
-      <c r="D29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>8</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="n">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>32</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" t="n">
         <v>0.4526941447419411</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" t="n">
         <v>128</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="L29" t="n">
         <v>0.001502900296524595</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="M29" t="n">
         <v>29</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="O29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P29" t="n">
         <v>0.5335694702867564</v>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="Q29" t="n">
         <v>0.3171811952727125</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="R29" t="n">
         <v>0.8933731490732737</v>
       </c>
-      <c r="S29" s="2" t="n">
+      <c r="S29" t="n">
         <v>0.8994429034785064</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="T29" t="n">
         <v>0.8933731490732737</v>
       </c>
-      <c r="U29" s="2" t="n">
+      <c r="U29" t="n">
         <v>0.8927242919042692</v>
       </c>
-      <c r="V29" s="2" t="n">
+      <c r="V29" t="n">
         <v>0.9805210784076335</v>
       </c>
-      <c r="W29" s="2" t="n">
+      <c r="W29" t="n">
         <v>0.5335694702867564</v>
       </c>
-      <c r="X29" s="2" t="n">
+      <c r="X29" t="n">
         <v>0.8894417094375197</v>
       </c>
-      <c r="Y29" s="2" t="n">
+      <c r="Y29" t="n">
         <v>0.8935509278571486</v>
       </c>
-      <c r="Z29" s="2" t="n">
+      <c r="Z29" t="n">
         <v>0.8894417094375197</v>
       </c>
-      <c r="AA29" s="2" t="n">
+      <c r="AA29" t="n">
         <v>0.8813942297890893</v>
       </c>
-      <c r="AB29" s="2" t="n">
+      <c r="AB29" t="n">
         <v>0.9620793900733482</v>
       </c>
-      <c r="AC29" s="2" t="n">
+      <c r="AC29" t="n">
         <v>0.2390158722715436</v>
       </c>
-      <c r="AD29" s="2" t="n">
+      <c r="AD29" t="n">
         <v>0.9344820362417513</v>
       </c>
-      <c r="AE29" s="2" t="n">
+      <c r="AE29" t="n">
         <v>0.9343272772938765</v>
       </c>
-      <c r="AF29" s="2" t="n">
+      <c r="AF29" t="n">
         <v>0.9344820362417513</v>
       </c>
-      <c r="AG29" s="2" t="n">
+      <c r="AG29" t="n">
         <v>0.9324290198880442</v>
       </c>
-      <c r="AH29" s="2" t="n">
+      <c r="AH29" t="n">
         <v>0.9861238747763847</v>
       </c>
-      <c r="AI29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ29" s="2" t="n">
+      <c r="AI29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>10</v>
       </c>
-      <c r="AK29" s="2" t="n">
+      <c r="AK29" t="n">
         <v>49.0435889970031</v>
       </c>
-      <c r="AL29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29" s="2" t="inlineStr">
+      <c r="AL29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="inlineStr">
         <is>
           <t>NVIDIA GeForce RTX 5060</t>
         </is>
       </c>
-      <c r="AN29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" s="2" t="n">
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
         <v>92000</v>
       </c>
-      <c r="AP29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" s="2" t="b">
-        <v>0</v>
+      <c r="AP29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="30">
@@ -4561,6 +5348,33 @@
       <c r="AQ30" t="b">
         <v>0</v>
       </c>
+      <c r="AR30" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4695,6 +5509,33 @@
       </c>
       <c r="AQ31" t="b">
         <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
